--- a/out/MLP-Mamba1_repeat_3_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.648249220197788</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003653019737068098</v>
+        <v>-0.0002556174543260131</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1572883166573085</v>
+        <v>0.1100614542579717</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3149966092169683</v>
+        <v>0.220416633438058</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6076887770636877</v>
+        <v>0.4252256041575488</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.373487859579517</v>
+        <v>0.9610878428122648</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1869284743529056</v>
+        <v>0.1308017795310258</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.138886748510111</v>
+        <v>0.7969274979848575</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03792897137689699</v>
+        <v>0.02654065405533219</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.648249220197788</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.027524198965062</v>
+        <v>0.7190023996632446</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03284853267356672</v>
+        <v>0.02298502816703271</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.055249948361402</v>
+        <v>0.7384031773793388</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.016058552286149</v>
+        <v>0.0112372084466643</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.648249220197788</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.054476849179105</v>
+        <v>0.7378622009973514</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00766293740906623</v>
+        <v>0.005360418037190818</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.053723936940665</v>
+        <v>0.7373338614061838</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003189403145047368</v>
+        <v>0.002230191465208292</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.648249220197788</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.052430890768723</v>
+        <v>0.7364275547385148</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002208925504884944</v>
+        <v>0.001544516351972453</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.053656661482793</v>
+        <v>0.7372838149103499</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009195518789583747</v>
+        <v>0.0006418641717590301</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.053283660539434</v>
+        <v>0.737021342473324</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004740790451638625</v>
+        <v>0.0003304221487758145</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.053311972069058</v>
+        <v>0.7370396484473862</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001834262070356334</v>
+        <v>0.0001267408856990083</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.053203512739122</v>
+        <v>0.7369623133726958</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.750135377912412e-05</v>
+        <v>6.657915766698612e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.053215452364957</v>
+        <v>0.7369691571484726</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.582045589694517e-05</v>
+        <v>3.057431912786162e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.053208902730245</v>
+        <v>0.7369630724041744</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.897715270190287e-05</v>
+        <v>1.151759408353309e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.053200977439142</v>
+        <v>0.7369560253192582</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.145780771925869e-06</v>
+        <v>2.378749652309724e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.053192723810125</v>
+        <v>0.7369487112180461</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.525705377792857e-07</v>
+        <v>-1.69277857293039e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.053186611762519</v>
+        <v>0.7369429372391091</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.09281402832566e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.053180458048218</v>
+        <v>0.7369371680962415</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.053174642546065</v>
+        <v>0.7369316244281391</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.053169761247815</v>
+        <v>0.7369267032744177</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.053164840046267</v>
+        <v>0.7369267431298899</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.053164832075173</v>
+        <v>0.7369267351587955</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.053164991497062</v>
+        <v>0.7369268945806846</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.053164895843929</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.053165246572085</v>
+        <v>0.7369271496557074</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.053164999468157</v>
+        <v>0.7369269025517791</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.053164959612684</v>
+        <v>0.7369268626963068</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.053164895843929</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.053164967583779</v>
+        <v>0.7369268706674013</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.053164895843929</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.248249220197788</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.053164999468157</v>
+        <v>0.7369269025517791</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.05316509512129</v>
+        <v>0.7369269982049128</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.053165031352534</v>
+        <v>0.7369269344361569</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.053164991497062</v>
+        <v>0.7369268945806846</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.053164967583779</v>
+        <v>0.7369268706674013</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.053164720479851</v>
+        <v>0.7369266235634732</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.053164640768906</v>
+        <v>0.7369265438525283</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.053164688595473</v>
+        <v>0.736926591679095</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.05316480816189</v>
+        <v>0.7369267112455121</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.053164792219701</v>
+        <v>0.7369266953033232</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.05316480816189</v>
+        <v>0.7369267112455121</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.053164792219701</v>
+        <v>0.7369266953033232</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.053164848017362</v>
+        <v>0.7369267511009844</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.053164848017362</v>
+        <v>0.7369267511009844</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.248249220197788</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.053164848017362</v>
+        <v>0.7369267511009844</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.053164999468157</v>
+        <v>0.7369269025517791</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.053165214687707</v>
+        <v>0.7369271177713296</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.053165127005668</v>
+        <v>0.7369270300892906</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.053165079179101</v>
+        <v>0.7369269822627238</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.053165127005668</v>
+        <v>0.7369270300892906</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.053164943670496</v>
+        <v>0.7369268467541179</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.05316495164159</v>
+        <v>0.7369268547252124</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.053164959612684</v>
+        <v>0.7369268626963068</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.053164967583779</v>
+        <v>0.7369268706674013</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.053164967583779</v>
+        <v>0.7369268706674013</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>3.248249220197788</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.053165007439251</v>
+        <v>0.7369269105228735</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.248249220197788</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.053165071208007</v>
+        <v>0.7369269742916293</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.053165182803329</v>
+        <v>0.7369270858869518</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.053165230629896</v>
+        <v>0.7369271337135185</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.053165190774424</v>
+        <v>0.7369270938580462</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>3.248249220197788</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.053165119034574</v>
+        <v>0.7369270221181962</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.05316523860099</v>
+        <v>0.7369271416846129</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.053165079179101</v>
+        <v>0.7369269822627238</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.053164848017362</v>
+        <v>0.7369267511009844</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.053164800190795</v>
+        <v>0.7369267032744177</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.053164832075173</v>
+        <v>0.7369267351587955</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.053164895843929</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.053164895843929</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.053164816132984</v>
+        <v>0.7369267192166066</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.053164696566567</v>
+        <v>0.7369265996501895</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.053164656711095</v>
+        <v>0.7369265597947172</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.053164800190795</v>
+        <v>0.7369267032744177</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.053164935699401</v>
+        <v>0.7369268387830235</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.053164919757212</v>
+        <v>0.7369268228408346</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.053164895843929</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.053164855988456</v>
+        <v>0.7369267590720788</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.053164752364228</v>
+        <v>0.736926655447851</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>3.248249220197788</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.053164632797811</v>
+        <v>0.7369265358814339</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.053164752364228</v>
+        <v>0.736926655447851</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.053164800190795</v>
+        <v>0.7369267032744177</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.053164895843929</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.053164776277512</v>
+        <v>0.7369266793611343</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.053164784248606</v>
+        <v>0.7369266873322288</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_3_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.7428964315819336</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307028</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003653019737068098</v>
+        <v>-0.0002781876025688835</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1572883166573085</v>
+        <v>0.1197793977163494</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3149966092169683</v>
+        <v>0.2398786699474316</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6076887770636877</v>
+        <v>0.4627719864806611</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.373487859579517</v>
+        <v>1.045949338175913</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1869284743529056</v>
+        <v>0.1423512572078116</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.138886748510111</v>
+        <v>0.8672940358273215</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03792897137689699</v>
+        <v>0.02888392242389911</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307029</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.027524198965062</v>
+        <v>0.7824883423234501</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03284853267356672</v>
+        <v>0.02501511829218049</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.055249948361402</v>
+        <v>0.8036023113333022</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.016058552286149</v>
+        <v>0.01222932360620418</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307029</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.054476849179105</v>
+        <v>0.8030135730118556</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00766293740906623</v>
+        <v>0.005834151709465822</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.053723936940665</v>
+        <v>0.8024390285434632</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003189403145047368</v>
+        <v>0.00242782358728773</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307029</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.052430890768723</v>
+        <v>0.8014531512168991</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002208925504884944</v>
+        <v>0.001681102205707076</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.053656661482793</v>
+        <v>0.8023853292425264</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009195518789583747</v>
+        <v>0.000698561429841495</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>3.248249220197788</v>
+        <v>0.3299763727307029</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.053283660539434</v>
+        <v>0.8021001619627516</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004740790451638625</v>
+        <v>0.0003598216996645313</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.329976372730703</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.053311972069058</v>
+        <v>0.8021205346047959</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001834262070356334</v>
+        <v>0.0001382878956009135</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.053203512739122</v>
+        <v>0.8020367159243366</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.750135377912412e-05</v>
+        <v>7.345075680301679e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.053215452364957</v>
+        <v>0.8020446442846705</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.582045589694517e-05</v>
+        <v>3.339767778880302e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.053208902730245</v>
+        <v>0.8020384654784606</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.897715270190287e-05</v>
+        <v>1.311607093032661e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.053200977439142</v>
+        <v>0.8020312233741377</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.145780771925869e-06</v>
+        <v>2.839921505579082e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.053192723810125</v>
+        <v>0.8020236929017496</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.525705377792857e-07</v>
+        <v>-1.279375894546688e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.053186611762519</v>
+        <v>0.8020178221754455</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.09281402832566e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.053180458048218</v>
+        <v>0.8020119573794443</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.053174642546065</v>
+        <v>0.8020062782027361</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.053169761247815</v>
+        <v>0.8020013969044867</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.053164840046267</v>
+        <v>0.8019964757029389</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.248249220197788</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.053164832075173</v>
+        <v>0.8019964677318444</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.053164991497062</v>
+        <v>0.8019966271537335</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.248249220197788</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.053164895843929</v>
+        <v>0.8019965315006</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.053165246572085</v>
+        <v>0.8019968822287563</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.053164999468157</v>
+        <v>0.801996635124828</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.053164959612684</v>
+        <v>0.8019965952693557</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.053164895843929</v>
+        <v>0.8019965315006</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.053164967583779</v>
+        <v>0.8019966032404502</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.329976372730703</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.053164895843929</v>
+        <v>0.8019965315006</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.248249220197788</v>
+        <v>0.329976372730703</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.053164999468157</v>
+        <v>0.801996635124828</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.05316509512129</v>
+        <v>0.8019967307779616</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.053165031352534</v>
+        <v>0.8019966670092058</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.053164991497062</v>
+        <v>0.8019966271537335</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.053164967583779</v>
+        <v>0.8019966032404502</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.053164720479851</v>
+        <v>0.801996356136522</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.053164640768906</v>
+        <v>0.8019962764255772</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.053164688595473</v>
+        <v>0.801996324252144</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.05316480816189</v>
+        <v>0.8019964438185611</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.053164792219701</v>
+        <v>0.8019964278763722</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.05316480816189</v>
+        <v>0.8019964438185611</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.053164792219701</v>
+        <v>0.8019964278763722</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.053164848017362</v>
+        <v>0.8019964836740333</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.053164848017362</v>
+        <v>0.8019964836740333</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.248249220197788</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.053164848017362</v>
+        <v>0.8019964836740333</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.053164999468157</v>
+        <v>0.801996635124828</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.248249220197788</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.053165214687707</v>
+        <v>0.8019968503443785</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.053165127005668</v>
+        <v>0.8019967626623394</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.053165079179101</v>
+        <v>0.8019967148357727</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.053165127005668</v>
+        <v>0.8019967626623394</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.053164943670496</v>
+        <v>0.8019965793271667</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.05316495164159</v>
+        <v>0.8019965872982613</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.053164959612684</v>
+        <v>0.8019965952693557</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.053164967583779</v>
+        <v>0.8019966032404502</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.329976372730703</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.053164967583779</v>
+        <v>0.8019966032404502</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.053165007439251</v>
+        <v>0.8019966430959224</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.053165071208007</v>
+        <v>0.8019967068646783</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.053165182803329</v>
+        <v>0.8019968184600007</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.053165230629896</v>
+        <v>0.8019968662865674</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307029</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.053165190774424</v>
+        <v>0.8019968264310952</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>3.248249220197788</v>
+        <v>0.3299763727307029</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.053165119034574</v>
+        <v>0.801996754691245</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.05316523860099</v>
+        <v>0.8019968742576619</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.053165079179101</v>
+        <v>0.8019967148357727</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.053164848017362</v>
+        <v>0.8019964836740333</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.053164800190795</v>
+        <v>0.8019964358474666</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.053164832075173</v>
+        <v>0.8019964677318444</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.053164895843929</v>
+        <v>0.8019965315006</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.053164895843929</v>
+        <v>0.8019965315006</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.053164816132984</v>
+        <v>0.8019964517896555</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.053164696566567</v>
+        <v>0.8019963322232384</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.053164656711095</v>
+        <v>0.8019962923677662</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.053164800190795</v>
+        <v>0.8019964358474666</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.053164935699401</v>
+        <v>0.8019965713560723</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.053164919757212</v>
+        <v>0.8019965554138834</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.053164895843929</v>
+        <v>0.8019965315006</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.053164855988456</v>
+        <v>0.8019964916451278</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.053164752364228</v>
+        <v>0.8019963880208999</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>3.248249220197788</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.053164632797811</v>
+        <v>0.8019962684544828</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.053164752364228</v>
+        <v>0.8019963880208999</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.053164800190795</v>
+        <v>0.8019964358474666</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.053164895843929</v>
+        <v>0.8019965315006</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.053164776277512</v>
+        <v>0.8019964119341833</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.053164784248606</v>
+        <v>0.8019964199052777</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_3_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4243833720684052</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7428964315819336</v>
+        <v>0.1199999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5118559002876282</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.3299763727307028</v>
+        <v>-0.1600000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4264027774333954</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.3735580146312714</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.2958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4011853635311127</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4106683731079102</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4124296605587006</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4208326041698456</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4768969714641571</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3879879415035248</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3799538016319275</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3952394425868988</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4917177259922028</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.529976372730703</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.5061303377151489</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.355816490433165</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5554395318031311</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.355816490433165</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4900008738040924</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4207722544670105</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4413782954216003</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4609042108058929</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3814311623573303</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3447319567203522</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3358107209205627</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3187558054924011</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4783096611499786</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3932140469551086</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3823314905166626</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3790837526321411</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4100684821605682</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4293035268783569</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.344625860452652</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4358548521995544</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.285515308380127</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.465126633644104</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.3818083703517914</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.425460010766983</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4281255900859833</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4844076335430145</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5346996188163757</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.355816490433165</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.6714532375335693</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.181656608135626</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5549467206001282</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.181656608135626</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.8605201840400696</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.181656608135626</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.7111968994140625</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.181656608135626</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002781876025688835</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1197793977163494</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9477192163467407</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.181656608135626</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2398786699474316</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4627719864806611</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.8899521231651306</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.355816490433165</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.045949338175913</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1423512572078116</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.03862154483795166</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.355816490433165</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8672940358273215</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02888392242389911</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.7678144574165344</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3299763727307029</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7824883423234501</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02501511829218049</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.2400362491607666</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8036023113333022</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01222932360620418</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.6171303987503052</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3299763727307029</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8030135730118556</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005834151709465822</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4118757843971252</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8024390285434632</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00242782358728773</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5766845345497131</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.3299763727307029</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8014531512168991</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001681102205707076</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3513156473636627</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8023853292425264</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000698561429841495</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5641855597496033</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.3299763727307029</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8021001619627516</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003598216996645313</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3499093651771545</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.329976372730703</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8021205346047959</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001382878956009135</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.3978601098060608</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8020367159243366</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.345075680301679e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4243046343326569</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8020446442846705</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.339767778880302e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.2944527566432953</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8020384654784606</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.311607093032661e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3367339968681335</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8020312233741377</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.839921505579082e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.3135603666305542</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8020236929017496</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3114579021930695</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8020178221754455</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.2516374886035919</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8020119573794443</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4031297564506531</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8020062782027361</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4586869478225708</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8020013969044867</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3562617003917694</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.529976372730703</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8019964757029389</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5703925490379333</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.529976372730703</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8019964677318444</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.322355329990387</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.355816490433165</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8019966271537335</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.7316482663154602</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.529976372730703</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8019965315006</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3248778581619263</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.529976372730703</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8019968822287563</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3045493960380554</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.801996635124828</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.417199045419693</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8019965952693557</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4270088672637939</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8019965315006</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3266303837299347</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8019966032404502</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3105859458446503</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.329976372730703</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8019965315006</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.8019677400588989</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.329976372730703</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.801996635124828</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4498273432254791</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.529976372730703</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8019967307779616</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3225517272949219</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8019966670092058</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3036060035228729</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8019966271537335</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.2057260125875473</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8019966032404502</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2750739455223083</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.801996356136522</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3850230574607849</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8019962764255772</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4210205078125</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.801996324252144</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.2811636030673981</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8019964438185611</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.3830470144748688</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8019964278763722</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.345461368560791</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8019964438185611</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4394590854644775</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8019964278763722</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3437631130218506</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8019964836740333</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3074136972427368</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.529976372730703</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8019964836740333</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.6166225075721741</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.529976372730703</v>
+        <v>0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8019964836740333</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3872098922729492</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.355816490433165</v>
+        <v>0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.801996635124828</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.5628120303153992</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.529976372730703</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8019968503443785</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3330921828746796</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.529976372730703</v>
+        <v>0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8019967626623394</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4742099046707153</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8019967148357727</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.2031191140413284</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8019967626623394</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3557896614074707</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8019965793271667</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3145348429679871</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8019965872982613</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4702833592891693</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8019965952693557</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2929594218730927</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8019966032404502</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3670578002929688</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.329976372730703</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8019966032404502</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.5448362827301025</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.355816490433165</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8019966430959224</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5078948140144348</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.355816490433165</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8019967068646783</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4752894043922424</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8019968184600007</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3261476457118988</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8019968662865674</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3389039635658264</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3299763727307029</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8019968264310952</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.5107768177986145</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3299763727307029</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.801996754691245</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2340106517076492</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.5299763727307029</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8019968742576619</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.2424639612436295</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8019967148357727</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3149859309196472</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8019964836740333</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3724775314331055</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8019964358474666</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3743839859962463</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8019964677318444</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.355404257774353</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8019965315006</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2371412515640259</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8019965315006</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2447247952222824</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8019964517896555</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2488660663366318</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8019963322232384</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.479003369808197</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8019962923677662</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4507691264152527</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8019964358474666</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3999665379524231</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8019965713560723</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2309921085834503</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8019965554138834</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.2986834049224854</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8019965315006</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.2603453397750854</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8019964916451278</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.197170078754425</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5299763727307029</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8019963880208999</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.5936161875724792</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5299763727307029</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8019962684544828</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3409211039543152</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5299763727307029</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8019963880208999</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4684861600399017</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8019964358474666</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.2455743104219437</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.2958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8019965315006</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3413340449333191</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8019964119341833</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4079850316047668</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8019964199052777</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_3_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.4243833720684052</v>
+        <v>0.4243834614753723</v>
       </c>
       <c r="JB2" t="n">
         <v>0.1199999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.5118559002876282</v>
+        <v>0.5118559598922729</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.1600000000000002</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.4264027774333954</v>
+        <v>0.4264028668403625</v>
       </c>
       <c r="JB4" t="n">
         <v>0.16</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.3735580146312714</v>
+        <v>0.3735580742359161</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.4011853635311127</v>
+        <v>0.4011854529380798</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.5799999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.4124296605587006</v>
+        <v>0.4124298095703125</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.4208326041698456</v>
+        <v>0.4208327829837799</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.3</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4768969714641571</v>
+        <v>0.4768970608711243</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.3879879415035248</v>
+        <v>0.3879881799221039</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.5799999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.3799538016319275</v>
+        <v>0.3799539506435394</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.4399999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.3952394425868988</v>
+        <v>0.3952396810054779</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.4399999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.4917177259922028</v>
+        <v>0.4917178452014923</v>
       </c>
       <c r="JB14" t="n">
         <v>0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.5061303377151489</v>
+        <v>0.5061304569244385</v>
       </c>
       <c r="JB15" t="n">
         <v>0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.5554395318031311</v>
+        <v>0.5554395914077759</v>
       </c>
       <c r="JB16" t="n">
         <v>0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4207722544670105</v>
+        <v>0.4207723140716553</v>
       </c>
       <c r="JB18" t="n">
         <v>0.4399999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.4413782954216003</v>
+        <v>0.4413783848285675</v>
       </c>
       <c r="JB19" t="n">
         <v>0.16</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.4609042108058929</v>
+        <v>0.4609043300151825</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.3814311623573303</v>
+        <v>0.3814308345317841</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.3447319567203522</v>
+        <v>0.3447315990924835</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.8599999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.3358107209205627</v>
+        <v>0.3358107805252075</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.7199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3187558054924011</v>
+        <v>0.3187558650970459</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.7199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.4783096611499786</v>
+        <v>0.4783097505569458</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.3932140469551086</v>
+        <v>0.3932141065597534</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.3823314905166626</v>
+        <v>0.3823315501213074</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.3790837526321411</v>
+        <v>0.3790838122367859</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.8599999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.4100684821605682</v>
+        <v>0.410068690776825</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.8599999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.4293035268783569</v>
+        <v>0.4293036460876465</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.344625860452652</v>
+        <v>0.3446258902549744</v>
       </c>
       <c r="JB31" t="n">
         <v>0.02000000000000007</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4358548521995544</v>
+        <v>0.4358549416065216</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.465126633644104</v>
+        <v>0.4651268422603607</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.3818083703517914</v>
+        <v>0.3818085491657257</v>
       </c>
       <c r="JB35" t="n">
         <v>0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.425460010766983</v>
+        <v>0.4254602789878845</v>
       </c>
       <c r="JB36" t="n">
         <v>0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.4281255900859833</v>
+        <v>0.4281257092952728</v>
       </c>
       <c r="JB37" t="n">
         <v>0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.4844076335430145</v>
+        <v>0.4844077527523041</v>
       </c>
       <c r="JB38" t="n">
         <v>0.8599999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.5346996188163757</v>
+        <v>0.5346996784210205</v>
       </c>
       <c r="JB39" t="n">
         <v>0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.6714532375335693</v>
+        <v>0.6714533567428589</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.5549467206001282</v>
+        <v>0.5549466013908386</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.8605201840400696</v>
+        <v>0.8605200052261353</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.7111968994140625</v>
+        <v>0.7111979126930237</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.9477192163467407</v>
+        <v>0.9477196931838989</v>
       </c>
       <c r="JB44" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.8899521231651306</v>
+        <v>0.889953076839447</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.02000000000000007</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.03862154483795166</v>
+        <v>0.03862179815769196</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.7678144574165344</v>
+        <v>0.7678152918815613</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.2400362491607666</v>
+        <v>0.2400365471839905</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.6171303987503052</v>
+        <v>0.6171309351921082</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.4399999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.4118757843971252</v>
+        <v>0.4118761718273163</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.5799999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.5766845345497131</v>
+        <v>0.5766848921775818</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.3</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.3513156473636627</v>
+        <v>0.351315826177597</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.5641855597496033</v>
+        <v>0.5641862750053406</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.4399999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.3499093651771545</v>
+        <v>0.3499100506305695</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.7199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.3978601098060608</v>
+        <v>0.3978602588176727</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.7199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.4243046343326569</v>
+        <v>0.4243048131465912</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.2944527566432953</v>
+        <v>0.2944527864456177</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.3367339968681335</v>
+        <v>0.3367340564727783</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.3135603666305542</v>
+        <v>0.3135603964328766</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.3114579021930695</v>
+        <v>0.3114579916000366</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.2516374886035919</v>
+        <v>0.2516376674175262</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.4586869478225708</v>
+        <v>0.4586871862411499</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.1199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.3562617003917694</v>
+        <v>0.3562617599964142</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.1199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.5703925490379333</v>
+        <v>0.5703927278518677</v>
       </c>
       <c r="JB65" t="n">
         <v>0.1600000000000001</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.322355329990387</v>
+        <v>0.3223554790019989</v>
       </c>
       <c r="JB66" t="n">
         <v>0.16</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.7316482663154602</v>
+        <v>0.7316486239433289</v>
       </c>
       <c r="JB67" t="n">
         <v>0.1600000000000001</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.3248778581619263</v>
+        <v>0.3248781859874725</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.3045493960380554</v>
+        <v>0.3045495748519897</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.1199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.417199045419693</v>
+        <v>0.4171993136405945</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.3266303837299347</v>
+        <v>0.3266304135322571</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.8019677400588989</v>
+        <v>0.8019686341285706</v>
       </c>
       <c r="JB74" t="n">
         <v>0.1600000000000001</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.4498273432254791</v>
+        <v>0.4498279392719269</v>
       </c>
       <c r="JB75" t="n">
         <v>0.1600000000000001</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.3225517272949219</v>
+        <v>0.322551816701889</v>
       </c>
       <c r="JB76" t="n">
         <v>0.16</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.2057260125875473</v>
+        <v>0.2057261914014816</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.2750739455223083</v>
+        <v>0.2750740051269531</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.7199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.3850230574607849</v>
+        <v>0.385022908449173</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.7199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.2811636030673981</v>
+        <v>0.2811635434627533</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.3830470144748688</v>
+        <v>0.3830469846725464</v>
       </c>
       <c r="JB83" t="n">
         <v>0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3074136972427368</v>
+        <v>0.3074136674404144</v>
       </c>
       <c r="JB87" t="n">
         <v>0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.6166225075721741</v>
+        <v>0.6166228055953979</v>
       </c>
       <c r="JB88" t="n">
         <v>0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.5628120303153992</v>
+        <v>0.5628125071525574</v>
       </c>
       <c r="JB90" t="n">
         <v>0.5799999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.3330921828746796</v>
+        <v>0.333092212677002</v>
       </c>
       <c r="JB91" t="n">
         <v>0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.2031191140413284</v>
+        <v>0.2031191885471344</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.2929594218730927</v>
+        <v>0.2929593920707703</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.5448362827301025</v>
+        <v>0.5448364615440369</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.5078948140144348</v>
+        <v>0.5078949332237244</v>
       </c>
       <c r="JB100" t="n">
         <v>0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.4752894043922424</v>
+        <v>0.4752895534038544</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.3389039635658264</v>
+        <v>0.338904082775116</v>
       </c>
       <c r="JB103" t="n">
         <v>0.02000000000000007</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.5107768177986145</v>
+        <v>0.5107769370079041</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.2340106517076492</v>
+        <v>0.2340107560157776</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.8599999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.2424639612436295</v>
+        <v>0.2424642443656921</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.8599999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.3743839859962463</v>
+        <v>0.3743839263916016</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.2371412515640259</v>
+        <v>0.2371411919593811</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.2488660663366318</v>
+        <v>0.248866006731987</v>
       </c>
       <c r="JB113" t="n">
         <v>0.16</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.479003369808197</v>
+        <v>0.4790033102035522</v>
       </c>
       <c r="JB114" t="n">
         <v>0.4399999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.2986834049224854</v>
+        <v>0.2986833453178406</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.1199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.197170078754425</v>
+        <v>0.1971701383590698</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.5936161875724792</v>
+        <v>0.5936163663864136</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.4684861600399017</v>
+        <v>0.4684861898422241</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.2455743104219437</v>
+        <v>0.2455742508172989</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.5799999999999998</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.4079850316047668</v>
+        <v>0.407985121011734</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.5799999999999998</v>
